--- a/교육자료/양식/_담당자용/01_브랜드배정표.xlsx
+++ b/교육자료/양식/_담당자용/01_브랜드배정표.xlsx
@@ -502,7 +502,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>※ 이번 교육 주력 6개. 1인 1~2개가 현실적입니다. 원고에는 「홍보성 / 정보성」 두 방향이 있고, 브랜드와 관계없이 둘 다 나옵니다.</t>
+          <t>※ 이번 교육 4명 / 1인 1브랜드 — 퍼스트디자인·하오디자인·하오스튜디오·윈차이나에 배정. 하오팩토리·레드트랜스는 설명만 하고 미배정. 원고에는 「홍보성 / 정보성」 두 방향이 있고, 브랜드와 관계없이 둘 다 나옵니다.</t>
         </is>
       </c>
     </row>
